--- a/data/2.full_abstracting/26_03_01_fullabstracting.xlsx
+++ b/data/2.full_abstracting/26_03_01_fullabstracting.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>10.1016/j.socec.2026.102530</t>
+          <t>https://doi.org/10.1016/j.socec.2026.102530</t>
         </is>
       </c>
       <c r="D2">
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>10.1093/sw/swag005</t>
+          <t>https://doi.org/10.1093/sw/swag005</t>
         </is>
       </c>
       <c r="D4">
@@ -524,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>10.1080/00223891.2026.2621759</t>
+          <t>https://doi.org/10.1080/00223891.2026.2621759</t>
         </is>
       </c>
       <c r="D5">
